--- a/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Hogares con temperatura insuficiente (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,68; 40,36</t>
+          <t>25,95; 39,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,09; 37,3</t>
+          <t>21,13; 37,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,51; 35,74</t>
+          <t>25,37; 36,35</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,78; 50,58</t>
+          <t>36,99; 50,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,84; 48,94</t>
+          <t>37,19; 48,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,66; 47,38</t>
+          <t>38,53; 47,26</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,46; 36,15</t>
+          <t>17,58; 36,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,46; 35,74</t>
+          <t>22,87; 35,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,75; 33,7</t>
+          <t>21,78; 33,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,04; 56,34</t>
+          <t>43,91; 56,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,2; 53,82</t>
+          <t>40,56; 54,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,88; 53,17</t>
+          <t>43,66; 53,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,36; 43,02</t>
+          <t>32,78; 42,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,15; 41,1</t>
+          <t>34,22; 40,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,34; 41,14</t>
+          <t>35,16; 40,67</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con temperatura insuficiente (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38869</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>40522</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>79392</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30435; 46517</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>29664; 52335</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>65377; 93672</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82611</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>108680</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>191291</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>70093; 96086</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>94844; 124671</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>171300; 210103</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54035</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>53588</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>107623</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33477; 68892</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>42377; 66185</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>81808; 126909</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>83848</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>84462</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>168310</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>73427; 95175</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>73132; 97360</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>151714; 185186</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>259364</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>287252</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>546616</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>217779; 282519</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>260441; 311256</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>501221; 579720</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,87; 41,35</t>
+          <t>23,94; 40,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 37,14</t>
+          <t>27,18; 41,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 36,27</t>
+          <t>26,29; 37,77</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,88; 49,87</t>
+          <t>38,81; 50,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 48,33</t>
+          <t>39,28; 51,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,72; 47,61</t>
+          <t>40,56; 49,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,0; 36,1</t>
+          <t>22,44; 35,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,36; 35,87</t>
+          <t>25,65; 38,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,79; 34,32</t>
+          <t>25,26; 34,88</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,6; 56,58</t>
+          <t>40,85; 54,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,79; 53,38</t>
+          <t>44,03; 57,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,52; 53,47</t>
+          <t>44,27; 53,65</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,25; 42,76</t>
+          <t>35,49; 42,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,67; 41,28</t>
+          <t>38,17; 44,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,35; 40,8</t>
+          <t>37,59; 42,49</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38869</t>
+          <t>39555</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79392</t>
+          <t>80605</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31508; 48490</t>
+          <t>30138; 50918</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29882; 52144</t>
+          <t>32911; 50404</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64704; 93462</t>
+          <t>64930; 93272</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82611</t>
+          <t>105771</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>108680</t>
+          <t>83306</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191291</t>
+          <t>189077</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69889; 94511</t>
+          <t>92058; 120830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93978; 123247</t>
+          <t>72006; 95135</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>172144; 211654</t>
+          <t>170566; 207647</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54035</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53588</t>
+          <t>50497</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107623</t>
+          <t>99011</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32361; 68743</t>
+          <t>37770; 60266</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41430; 66453</t>
+          <t>40281; 60559</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81854; 128942</t>
+          <t>82186; 113483</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>83848</t>
+          <t>79895</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>84462</t>
+          <t>84485</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168310</t>
+          <t>164380</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72905; 94616</t>
+          <t>68802; 91068</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71740; 96235</t>
+          <t>73272; 94948</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151240; 185828</t>
+          <t>148244; 179650</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>373</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>259364</t>
+          <t>273735</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>287252</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>546616</t>
+          <t>533073</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>227582; 284129</t>
+          <t>248371; 297023</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>263853; 314141</t>
+          <t>239667; 280734</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>503894; 581534</t>
+          <t>499121; 564113</t>
         </is>
       </c>
     </row>
